--- a/labeled/Add_Eating/July/multi_seed_results/seed_42/predictions.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_42/predictions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B146"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1162 +442,746 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40.47618865966797</v>
+        <v>30.55827713012695</v>
       </c>
       <c r="B2" t="n">
-        <v>40.0067024230957</v>
+        <v>25.36100769042969</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131.6999969482422</v>
+        <v>10.77075099945068</v>
       </c>
       <c r="B3" t="n">
-        <v>130.2887725830078</v>
+        <v>17.44803047180176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>39.5</v>
+        <v>31.29999923706055</v>
       </c>
       <c r="B4" t="n">
-        <v>50.45332336425781</v>
+        <v>30.99701499938965</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>40</v>
+        <v>21.23015785217285</v>
       </c>
       <c r="B5" t="n">
-        <v>39.29339218139648</v>
+        <v>38.59708404541016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>45.80952453613281</v>
+        <v>24.5714282989502</v>
       </c>
       <c r="B6" t="n">
-        <v>43.48154449462891</v>
+        <v>20.62419509887695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.4285717010498</v>
+        <v>19.60000038146973</v>
       </c>
       <c r="B7" t="n">
-        <v>11.50354099273682</v>
+        <v>21.23344612121582</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73.5</v>
+        <v>9.683794021606445</v>
       </c>
       <c r="B8" t="n">
-        <v>75.51237487792969</v>
+        <v>16.15275764465332</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.94444465637207</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B9" t="n">
-        <v>11.85770225524902</v>
+        <v>27.59098052978516</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17.10000038146973</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="B10" t="n">
-        <v>13.76704025268555</v>
+        <v>113.5166015625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9.486166000366211</v>
+        <v>40.09523773193359</v>
       </c>
       <c r="B11" t="n">
-        <v>9.580430030822754</v>
+        <v>27.02150535583496</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>33.90000152587891</v>
+        <v>8.275861740112305</v>
       </c>
       <c r="B12" t="n">
-        <v>18.62903785705566</v>
+        <v>32.51804351806641</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>36.23898315429688</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="B13" t="n">
-        <v>18.86666679382324</v>
+        <v>21.13345146179199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>33.79999923706055</v>
+        <v>11.65524005889893</v>
       </c>
       <c r="B14" t="n">
-        <v>31.31319618225098</v>
+        <v>16.27155494689941</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19.84127044677734</v>
+        <v>9.809523582458496</v>
       </c>
       <c r="B15" t="n">
-        <v>35.5977897644043</v>
+        <v>42.59469985961914</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>18.75</v>
+        <v>16.35651397705078</v>
       </c>
       <c r="B16" t="n">
-        <v>20.1868896484375</v>
+        <v>22.89285087585449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.5</v>
+        <v>11.11111068725586</v>
       </c>
       <c r="B17" t="n">
-        <v>50.45332336425781</v>
+        <v>16.29696273803711</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24.50396919250488</v>
+        <v>12.53672885894775</v>
       </c>
       <c r="B18" t="n">
-        <v>25.66837501525879</v>
+        <v>12.58718013763428</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>63.0476188659668</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B19" t="n">
-        <v>65.37310028076172</v>
+        <v>18.44021034240723</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13.71204662322998</v>
+        <v>25.46523094177246</v>
       </c>
       <c r="B20" t="n">
-        <v>14.51698970794678</v>
+        <v>26.73396682739258</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>59.40000152587891</v>
+        <v>15.51383399963379</v>
       </c>
       <c r="B21" t="n">
-        <v>53.05315780639648</v>
+        <v>28.52745246887207</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B22" t="n">
-        <v>20.77217674255371</v>
+        <v>8.968057632446289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10.83743858337402</v>
+        <v>58</v>
       </c>
       <c r="B23" t="n">
-        <v>11.11165618896484</v>
+        <v>52.26224517822266</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24.5714282989502</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B24" t="n">
-        <v>14.29867362976074</v>
+        <v>22.58065986633301</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>13.71204662322998</v>
       </c>
       <c r="B25" t="n">
-        <v>62.35440444946289</v>
+        <v>20.98125648498535</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26.28968238830566</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B26" t="n">
-        <v>24.01331329345703</v>
+        <v>37.35676193237305</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>21.82539749145508</v>
+        <v>41.52381134033203</v>
       </c>
       <c r="B27" t="n">
-        <v>25.17025566101074</v>
+        <v>35.40620803833008</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26.44466209411621</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B28" t="n">
-        <v>22.56130027770996</v>
+        <v>21.10527229309082</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>39.68254089355469</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="B29" t="n">
-        <v>35.08570861816406</v>
+        <v>35.2783088684082</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>46.5</v>
+        <v>16.38095283508301</v>
       </c>
       <c r="B30" t="n">
-        <v>39.32961273193359</v>
+        <v>42.09594345092773</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20.17629814147949</v>
+        <v>8.666666984558105</v>
       </c>
       <c r="B31" t="n">
-        <v>19.93263626098633</v>
+        <v>21.94218063354492</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2.938295841217041</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="B32" t="n">
-        <v>9.072612762451172</v>
+        <v>33.51517868041992</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32.41919708251953</v>
+        <v>6.660137176513672</v>
       </c>
       <c r="B33" t="n">
-        <v>29.54499244689941</v>
+        <v>14.67721557617188</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32.24206161499023</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="B34" t="n">
-        <v>31.18023681640625</v>
+        <v>51.5571403503418</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5.320197105407715</v>
+        <v>12.99603176116943</v>
       </c>
       <c r="B35" t="n">
-        <v>7.996598243713379</v>
+        <v>15.4780969619751</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27.32615089416504</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="B36" t="n">
-        <v>23.74552536010742</v>
+        <v>85.01345825195312</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>57.09999847412109</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="B37" t="n">
-        <v>57.2169075012207</v>
+        <v>30.14071655273438</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>30.66666603088379</v>
+        <v>60</v>
       </c>
       <c r="B38" t="n">
-        <v>19.19685745239258</v>
+        <v>64.41107940673828</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>27.90476226806641</v>
+        <v>27.18253898620605</v>
       </c>
       <c r="B39" t="n">
-        <v>22.39359474182129</v>
+        <v>19.41242408752441</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>25.79365158081055</v>
+        <v>24.50396919250488</v>
       </c>
       <c r="B40" t="n">
-        <v>17.48310661315918</v>
+        <v>27.34851837158203</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>19.58863830566406</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="B41" t="n">
-        <v>32.93426513671875</v>
+        <v>17.91454887390137</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>85.69999694824219</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B42" t="n">
-        <v>87.57380676269531</v>
+        <v>24.22232246398926</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38.09523773193359</v>
+        <v>21.84133148193359</v>
       </c>
       <c r="B43" t="n">
-        <v>31.38197898864746</v>
+        <v>22.95862197875977</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>22.09523773193359</v>
+        <v>23</v>
       </c>
       <c r="B44" t="n">
-        <v>27.26587867736816</v>
+        <v>26.57045555114746</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2.644466161727905</v>
+        <v>27.22820854187012</v>
       </c>
       <c r="B45" t="n">
-        <v>10.76352691650391</v>
+        <v>30.28387641906738</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>14.20176315307617</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B46" t="n">
-        <v>15.35393238067627</v>
+        <v>20.77670860290527</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>19.84127044677734</v>
+        <v>9.486166000366211</v>
       </c>
       <c r="B47" t="n">
-        <v>15.98274040222168</v>
+        <v>14.83611297607422</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22.6248779296875</v>
+        <v>18.84920692443848</v>
       </c>
       <c r="B48" t="n">
-        <v>15.77765655517578</v>
+        <v>41.35113906860352</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>80</v>
+        <v>2.154750347137451</v>
       </c>
       <c r="B49" t="n">
-        <v>83.61124420166016</v>
+        <v>11.54346370697021</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>15.118577003479</v>
+        <v>19.5</v>
       </c>
       <c r="B50" t="n">
-        <v>15.60023403167725</v>
+        <v>14.14912700653076</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>21.05778694152832</v>
+        <v>6.94444465637207</v>
       </c>
       <c r="B51" t="n">
-        <v>22.67733573913574</v>
+        <v>24.42949867248535</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>30.66666603088379</v>
+        <v>20.4761905670166</v>
       </c>
       <c r="B52" t="n">
-        <v>19.19685745239258</v>
+        <v>43.77339553833008</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>9.402546882629395</v>
+        <v>13.33333301544189</v>
       </c>
       <c r="B53" t="n">
-        <v>9.548500061035156</v>
+        <v>21.27464294433594</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>19.5</v>
+        <v>74.28571319580078</v>
       </c>
       <c r="B54" t="n">
-        <v>12.91611385345459</v>
+        <v>72.581787109375</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>13.10000038146973</v>
+        <v>36.23898315429688</v>
       </c>
       <c r="B55" t="n">
-        <v>16.27212905883789</v>
+        <v>23.82334136962891</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>21.13095283508301</v>
+        <v>26.44466209411621</v>
       </c>
       <c r="B56" t="n">
-        <v>12.78669834136963</v>
+        <v>22.30878067016602</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>39.68254089355469</v>
+        <v>18.55158805847168</v>
       </c>
       <c r="B57" t="n">
-        <v>40.14382934570312</v>
+        <v>20.41755485534668</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>36.63075256347656</v>
+        <v>9.142857551574707</v>
       </c>
       <c r="B58" t="n">
-        <v>19.69528961181641</v>
+        <v>31.22414970397949</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>25.39682579040527</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="B59" t="n">
-        <v>19.00925254821777</v>
+        <v>28.64777183532715</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>5.221674919128418</v>
+        <v>6.547618865966797</v>
       </c>
       <c r="B60" t="n">
-        <v>6.237728118896484</v>
+        <v>9.106752395629883</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>28.20763969421387</v>
+        <v>19.09892272949219</v>
       </c>
       <c r="B61" t="n">
-        <v>24.05165863037109</v>
+        <v>15.61800193786621</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>25.6611156463623</v>
+        <v>48</v>
       </c>
       <c r="B62" t="n">
-        <v>27.9930419921875</v>
+        <v>49.48762512207031</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>38.19047546386719</v>
+        <v>36.63075256347656</v>
       </c>
       <c r="B63" t="n">
-        <v>26.29729080200195</v>
+        <v>37.89855575561523</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>9.142857551574707</v>
+        <v>21.82539749145508</v>
       </c>
       <c r="B64" t="n">
-        <v>23.30160331726074</v>
+        <v>34.57430648803711</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>18.84920692443848</v>
+        <v>25.39682579040527</v>
       </c>
       <c r="B65" t="n">
-        <v>17.43333435058594</v>
+        <v>15.51514148712158</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>19.84127044677734</v>
+        <v>11.8095235824585</v>
       </c>
       <c r="B66" t="n">
-        <v>15.98274040222168</v>
+        <v>12.33496189117432</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20.37218475341797</v>
+        <v>26.05288887023926</v>
       </c>
       <c r="B67" t="n">
-        <v>18.34726142883301</v>
+        <v>38.3163948059082</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>40</v>
+        <v>18.19047546386719</v>
       </c>
       <c r="B68" t="n">
-        <v>53.23609161376953</v>
+        <v>19.83949661254883</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>30.55827713012695</v>
+        <v>44.46620941162109</v>
       </c>
       <c r="B69" t="n">
-        <v>22.89249420166016</v>
+        <v>28.42646026611328</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>10.77075099945068</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="B70" t="n">
-        <v>13.62001895904541</v>
+        <v>31.70338439941406</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>100</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B71" t="n">
-        <v>92.02734375</v>
+        <v>18.04146766662598</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>14.19999980926514</v>
+        <v>70.47618865966797</v>
       </c>
       <c r="B72" t="n">
-        <v>15.21714687347412</v>
+        <v>62.05241394042969</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25.09920692443848</v>
+        <v>31.80952453613281</v>
       </c>
       <c r="B73" t="n">
-        <v>24.00487899780273</v>
+        <v>33.83857727050781</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>9.683794021606445</v>
+        <v>13.4285717010498</v>
       </c>
       <c r="B74" t="n">
-        <v>11.03215026855469</v>
+        <v>20.29753494262695</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17.26190567016602</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="B75" t="n">
-        <v>17.77849388122559</v>
+        <v>27.9575309753418</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>76.19047546386719</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B76" t="n">
-        <v>78.4544677734375</v>
+        <v>20.56460952758789</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>40.09523773193359</v>
+        <v>37.21841430664062</v>
       </c>
       <c r="B77" t="n">
-        <v>15.05182647705078</v>
+        <v>39.34090423583984</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>39.17727661132812</v>
+        <v>3.428011655807495</v>
       </c>
       <c r="B78" t="n">
-        <v>40.20392227172852</v>
+        <v>9.843857765197754</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>11.65524005889893</v>
+        <v>18.65079307556152</v>
       </c>
       <c r="B79" t="n">
-        <v>15.4383020401001</v>
+        <v>16.10655784606934</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>19.74206352233887</v>
+        <v>24.87757110595703</v>
       </c>
       <c r="B80" t="n">
-        <v>15.58745956420898</v>
+        <v>27.05423927307129</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>14.22924900054932</v>
+        <v>41</v>
       </c>
       <c r="B81" t="n">
-        <v>13.28691577911377</v>
+        <v>47.98799896240234</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11.11111068725586</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B82" t="n">
-        <v>10.86752891540527</v>
+        <v>17.12896347045898</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>60</v>
+        <v>22.33104705810547</v>
       </c>
       <c r="B83" t="n">
-        <v>47.90490341186523</v>
+        <v>18.85626792907715</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>15.51383399963379</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B84" t="n">
-        <v>16.51411056518555</v>
+        <v>11.24855709075928</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>30.55827713012695</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="B85" t="n">
-        <v>22.89249420166016</v>
+        <v>16.7737865447998</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>58</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B86" t="n">
-        <v>59.52877044677734</v>
+        <v>23.19035720825195</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20.47012710571289</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B87" t="n">
-        <v>23.72003936767578</v>
+        <v>32.42918395996094</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>40</v>
+        <v>24.19047546386719</v>
       </c>
       <c r="B88" t="n">
-        <v>43.00653076171875</v>
+        <v>25.86288642883301</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>5.320197105407715</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B89" t="n">
-        <v>8.455820083618164</v>
+        <v>24.85715103149414</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>41.52381134033203</v>
+        <v>20.37218475341797</v>
       </c>
       <c r="B90" t="n">
-        <v>30.74653434753418</v>
+        <v>22.84467697143555</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>16.38095283508301</v>
+        <v>17.26190567016602</v>
       </c>
       <c r="B91" t="n">
-        <v>25.7667236328125</v>
+        <v>24.79677581787109</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>69.90476226806641</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B92" t="n">
-        <v>78.75160980224609</v>
+        <v>19.69238471984863</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>16.39999961853027</v>
+        <v>45</v>
       </c>
       <c r="B93" t="n">
-        <v>11.66095066070557</v>
+        <v>41.31824111938477</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>27.32615089416504</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B94" t="n">
-        <v>23.74552536010742</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>40.09523773193359</v>
-      </c>
-      <c r="B95" t="n">
-        <v>15.05182647705078</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>80.69999694824219</v>
-      </c>
-      <c r="B96" t="n">
-        <v>80.37085723876953</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>97.94319152832031</v>
-      </c>
-      <c r="B97" t="n">
-        <v>91.65326690673828</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>100</v>
-      </c>
-      <c r="B98" t="n">
-        <v>96.76332092285156</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>41.20000076293945</v>
-      </c>
-      <c r="B99" t="n">
-        <v>36.02363586425781</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>27.18253898620605</v>
-      </c>
-      <c r="B100" t="n">
-        <v>25.30900382995605</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>5.320197105407715</v>
-      </c>
-      <c r="B101" t="n">
-        <v>7.996598243713379</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>26.98412704467773</v>
-      </c>
-      <c r="B102" t="n">
-        <v>9.42266845703125</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>20</v>
-      </c>
-      <c r="B103" t="n">
-        <v>30.63005828857422</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
-        <v>79.36508178710938</v>
-      </c>
-      <c r="B104" t="n">
-        <v>68.86424255371094</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
-        <v>44.57143020629883</v>
-      </c>
-      <c r="B105" t="n">
-        <v>46.40521621704102</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>9.486166000366211</v>
-      </c>
-      <c r="B106" t="n">
-        <v>9.580430030822754</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>9.06403923034668</v>
-      </c>
-      <c r="B107" t="n">
-        <v>10.30573558807373</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>6.94444465637207</v>
-      </c>
-      <c r="B108" t="n">
-        <v>11.85770225524902</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>20.4761905670166</v>
-      </c>
-      <c r="B109" t="n">
-        <v>52.17670059204102</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>6.660137176513672</v>
-      </c>
-      <c r="B110" t="n">
-        <v>11.24960613250732</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>26.44466209411621</v>
-      </c>
-      <c r="B111" t="n">
-        <v>22.56130027770996</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>29.10000038146973</v>
-      </c>
-      <c r="B112" t="n">
-        <v>25.39392852783203</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>36.23898315429688</v>
-      </c>
-      <c r="B113" t="n">
-        <v>18.86666679382324</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>18.55158805847168</v>
-      </c>
-      <c r="B114" t="n">
-        <v>21.87573051452637</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>28.40352630615234</v>
-      </c>
-      <c r="B115" t="n">
-        <v>28.35574913024902</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>7.783251285552979</v>
-      </c>
-      <c r="B116" t="n">
-        <v>7.092171192169189</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>24.10000038146973</v>
-      </c>
-      <c r="B117" t="n">
-        <v>22.89772796630859</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>35.20000076293945</v>
-      </c>
-      <c r="B118" t="n">
-        <v>29.47230529785156</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>36.63075256347656</v>
-      </c>
-      <c r="B119" t="n">
-        <v>19.69528961181641</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>21.82539749145508</v>
-      </c>
-      <c r="B120" t="n">
-        <v>25.17025566101074</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>25.39682579040527</v>
-      </c>
-      <c r="B121" t="n">
-        <v>19.00925254821777</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>58</v>
-      </c>
-      <c r="B122" t="n">
-        <v>59.52877044677734</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
-        <v>15.08875751495361</v>
-      </c>
-      <c r="B123" t="n">
-        <v>13.91661262512207</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
-        <v>3.917727708816528</v>
-      </c>
-      <c r="B124" t="n">
-        <v>11.42361164093018</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>44.46620941162109</v>
-      </c>
-      <c r="B125" t="n">
-        <v>28.83352851867676</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>43.79999923706055</v>
-      </c>
-      <c r="B126" t="n">
-        <v>44.82100677490234</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>36.63075256347656</v>
-      </c>
-      <c r="B127" t="n">
-        <v>34.09925079345703</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>70.47618865966797</v>
-      </c>
-      <c r="B128" t="n">
-        <v>62.62284088134766</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>80</v>
-      </c>
-      <c r="B129" t="n">
-        <v>74.03855133056641</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>99.20635223388672</v>
-      </c>
-      <c r="B130" t="n">
-        <v>95.15341949462891</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>21.5475025177002</v>
-      </c>
-      <c r="B131" t="n">
-        <v>21.47046661376953</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>6.547618865966797</v>
-      </c>
-      <c r="B132" t="n">
-        <v>6.718834400177002</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>54.29999923706055</v>
-      </c>
-      <c r="B133" t="n">
-        <v>55.04146957397461</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>5.221674919128418</v>
-      </c>
-      <c r="B134" t="n">
-        <v>6.237728118896484</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>18.65079307556152</v>
-      </c>
-      <c r="B135" t="n">
-        <v>13.77467918395996</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>19.84127044677734</v>
-      </c>
-      <c r="B136" t="n">
-        <v>27.63549041748047</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>17.10000038146973</v>
-      </c>
-      <c r="B137" t="n">
-        <v>13.76704025268555</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>22.33104705810547</v>
-      </c>
-      <c r="B138" t="n">
-        <v>21.91628074645996</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>9.990205764770508</v>
-      </c>
-      <c r="B139" t="n">
-        <v>11.32892990112305</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>29.90476226806641</v>
-      </c>
-      <c r="B140" t="n">
-        <v>13.98872852325439</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>9.556650161743164</v>
-      </c>
-      <c r="B141" t="n">
-        <v>10.52655982971191</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>24.19047546386719</v>
-      </c>
-      <c r="B142" t="n">
-        <v>22.12474632263184</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>97.94319152832031</v>
-      </c>
-      <c r="B143" t="n">
-        <v>100.7023010253906</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>20.80867767333984</v>
-      </c>
-      <c r="B144" t="n">
-        <v>11.55765438079834</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>16.39999961853027</v>
-      </c>
-      <c r="B145" t="n">
-        <v>11.66095066070557</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>59.52381134033203</v>
-      </c>
-      <c r="B146" t="n">
-        <v>60.76792526245117</v>
+        <v>24.81458473205566</v>
       </c>
     </row>
   </sheetData>
